--- a/サンプル/絵コンテ_出力例_香盤表.xlsx
+++ b/サンプル/絵コンテ_出力例_香盤表.xlsx
@@ -44,7 +44,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,10 +136,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -837,15 +859,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -861,20 +888,45 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>ACTION/SE</t>
+          <t>ACTION</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
           <t>SCENARIO</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>小道具</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>カメラA</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>カメラB</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>機材</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
@@ -884,291 +936,398 @@
       <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="n">
-        <v>1</v>
-      </c>
+      <c r="B2" s="10" t="inlineStr"/>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>公園の全景
-2人が歩いてくる</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr"/>
-      <c r="E2" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>公園 / L / D</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-ロケ地: 代々木公園</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-カメラ: A 24mm</t>
-          </r>
-        </is>
-      </c>
+          <t>【公園 / L / D】　ロケ地: 代々木公園</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="11" t="n"/>
+      <c r="K2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>2人のミディアム
-花子が振り向く</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>花子「ねえ、聞いた？」
-太郎「何を？」</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>カメラ: A 50mm</t>
-        </is>
-      </c>
+          <t>公園の全景</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>24mm</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>倉庫の奥で男が拳銃を構える
-SE：雨音</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>倉庫 / LS / N</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-ロケ地: 湾岸倉庫</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-カメラ: A 35mm</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-機材: 三脚</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-小道具: 拳銃</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-備考: 雨降らし</t>
-          </r>
-        </is>
-      </c>
+      <c r="A4" s="12" t="inlineStr"/>
+      <c r="B4" s="12" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>2人が歩いてくる</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="12" t="inlineStr"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>拳銃のアップ</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="6" t="n">
+          <t>2人のミディアム</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>花子「ねえ、聞いた？」</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>50mm</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr"/>
+      <c r="B6" s="12" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>花子が振り向く</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>太郎「何を？」</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>カメラ: A 35mm
-機材: 三脚
-小道具: 拳銃
-備考: 雨降らし</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>【倉庫 / LS / N】　ロケ地: 湾岸倉庫</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>拳銃</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>35mm</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>三脚</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>備考: 雨降らし</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>倉庫の奥で男が拳銃を構える</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>雨音</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>車が入ってくる（PAN →）
-SE：エンジン音</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>男「来たか」</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>カメラ: A 85mm
-機材: 三脚、ドリー
-小道具: 拳銃、車
-備考: 雨降らし</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>3a</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>ヘッドライトのインサート</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>カメラ: A 35mm
-機材: 三脚
-小道具: 拳銃
-追加カット
-備考: 雨降らし</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>車内。後部座席から2人の後頭部</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>太郎「どこへ行く？」</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>車内 / S / N</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-カメラ: A 24mm</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-カメラ: B 50mm</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-機材: 車載リグ</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-2台撮り</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-備考: 劇用車</t>
-          </r>
-        </is>
-      </c>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
+          <t>拳銃のアップ</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>車が入ってくる（PAN →）</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>エンジン音</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>男「来たか」</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>車</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>85mm</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>ドリー</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>3a</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>ヘッドライトのインサート</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>追加カット</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>【車内 / S / N】</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>24mm</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>50mm</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>車載リグ</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>2台撮り</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="14" t="inlineStr"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>備考: 劇用車</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>車内。後部座席から2人の後頭部</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>太郎「どこへ行く？」</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
           <t>運転席の顔アップ</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>男「……」</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F15" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>カメラ: A 24mm
-カメラ: B 50mm
-機材: 車載リグ
-2台撮り
-備考: 劇用車</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="n">
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="F10" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
